--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SparklinesColumnGroup/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SparklinesColumnGroup/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R0a58d767b28840c8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rbd7323633c034fb6"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SparklinesColumnGroup/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SparklinesColumnGroup/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rbd7323633c034fb6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc131c3b10b944754"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SparklinesColumnGroup/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SparklinesColumnGroup/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc131c3b10b944754"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf83c3d5deaa64167"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SparklinesColumnGroup/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SparklinesColumnGroup/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf83c3d5deaa64167"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Reb232527e406412f"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SparklinesColumnGroup/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SparklinesColumnGroup/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Reb232527e406412f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R96fdbc30d19d4a31"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SparklinesColumnGroup/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SparklinesColumnGroup/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R96fdbc30d19d4a31"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R429dc3b3c66349c1"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SparklinesColumnGroup/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SparklinesColumnGroup/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R429dc3b3c66349c1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R37e336d37f03442e"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SparklinesColumnGroup/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SparklinesColumnGroup/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R37e336d37f03442e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7e37bb877347449c"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SparklinesColumnGroup/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SparklinesColumnGroup/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7e37bb877347449c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb3f1487313dc48f6"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SparklinesColumnGroup/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SparklinesColumnGroup/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb3f1487313dc48f6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rce8b4c20a30a48ef"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SparklinesColumnGroup/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SparklinesColumnGroup/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rce8b4c20a30a48ef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1c9ac13522dc4f72"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SparklinesColumnGroup/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SparklinesColumnGroup/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1c9ac13522dc4f72"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rcfa5a441830b4e7f"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SparklinesColumnGroup/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SparklinesColumnGroup/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rcfa5a441830b4e7f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R020fb5da97fd4d6d"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SparklinesColumnGroup/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SparklinesColumnGroup/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R020fb5da97fd4d6d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R72322c07956c47ff"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SparklinesColumnGroup/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SparklinesColumnGroup/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R72322c07956c47ff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R92567f8003674024"/>
   </x:sheets>
 </x:workbook>
 </file>
